--- a/02_plots/Flow_Results/outputs_IAEE_2025_run_2024_utilization_share.xlsx
+++ b/02_plots/Flow_Results/outputs_IAEE_2025_run_2024_utilization_share.xlsx
@@ -1,37 +1,121 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://studentcbs-my.sharepoint.com/personal/flv_eco_cbs_dk/Documents/Documents/03_LNG_Cap/hydrogen_grid/02_plots/Flow_Results/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_2B59D2BFD3F0DE4D373B2B11599320344057F95A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2607BFC6-CAD8-455D-8979-C873E56211F3}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="33645" yWindow="-28230" windowWidth="19440" windowHeight="30360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+  <si>
+    <t>Country</t>
+  </si>
+  <si>
+    <t>Flow</t>
+  </si>
+  <si>
+    <t>Capacity_tot</t>
+  </si>
+  <si>
+    <t>Share</t>
+  </si>
+  <si>
+    <t>EL</t>
+  </si>
+  <si>
+    <t>PL</t>
+  </si>
+  <si>
+    <t>UK</t>
+  </si>
+  <si>
+    <t>LV</t>
+  </si>
+  <si>
+    <t>HR</t>
+  </si>
+  <si>
+    <t>NL</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>FI</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>ES</t>
+  </si>
+  <si>
+    <t>EE</t>
+  </si>
+  <si>
+    <t>BE</t>
+  </si>
+  <si>
+    <t>LT</t>
+  </si>
+  <si>
+    <t>IE</t>
+  </si>
+  <si>
+    <t>FR</t>
+  </si>
+  <si>
+    <t>DE</t>
+  </si>
+  <si>
+    <t>TR</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +130,46 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="2">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -420,322 +457,274 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Flow</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Capacity_tot</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Share</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>EL</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2">
         <v>122125</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>122125</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>PL</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
         <v>81091</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>81091</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>64269.87580427225</v>
-      </c>
-      <c r="C4" t="n">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>64269.875804272247</v>
+      </c>
+      <c r="C4">
         <v>469937</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="2">
         <v>0.1367627486328428</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>LV</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>11108.45948084762</v>
-      </c>
-      <c r="C5" t="n">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5">
+        <v>11108.459480847619</v>
+      </c>
+      <c r="C5">
         <v>14655</v>
       </c>
-      <c r="D5" t="n">
-        <v>0.7579979174921611</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>HR</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+      <c r="D5" s="2">
+        <v>0.75799791749216106</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
         <v>25402</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>25402</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>NL</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" t="n">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
         <v>234480</v>
       </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>235871.546431326</v>
-      </c>
-      <c r="C8" t="n">
+      <c r="D7" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>235871.54643132599</v>
+      </c>
+      <c r="C8">
         <v>253531.5</v>
       </c>
-      <c r="D8" t="n">
-        <v>0.9303441443423243</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>FI</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>11669.45083333333</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="D8" s="2">
+        <v>0.93034414434232426</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9">
+        <v>11669.450833333331</v>
+      </c>
+      <c r="C9">
         <v>43965</v>
       </c>
-      <c r="D9" t="n">
-        <v>0.2654259259259258</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>PT</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>43774.39964126465</v>
-      </c>
-      <c r="C10" t="n">
+      <c r="D9" s="2">
+        <v>0.26542592592592579</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10">
+        <v>43774.399641264652</v>
+      </c>
+      <c r="C10">
         <v>74252</v>
       </c>
-      <c r="D10" t="n">
-        <v>0.5895383241025784</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>162993.2216790809</v>
-      </c>
-      <c r="C11" t="n">
+      <c r="D10" s="2">
+        <v>0.58953832410257845</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11">
+        <v>162993.22167908089</v>
+      </c>
+      <c r="C11">
         <v>655567</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="2">
         <v>0.2486293875059008</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>BE</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13">
         <v>139365.0872146152</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>149481</v>
       </c>
-      <c r="D13" t="n">
-        <v>0.9323264308816184</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>LT</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>36488.54855814494</v>
-      </c>
-      <c r="C14" t="n">
+      <c r="D13" s="2">
+        <v>0.93232643088161837</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14">
+        <v>36488.548558144939</v>
+      </c>
+      <c r="C14">
         <v>39080</v>
       </c>
-      <c r="D14" t="n">
-        <v>0.9336885506178336</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>IE</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>357542.0326588965</v>
-      </c>
-      <c r="C16" t="n">
+      <c r="D14" s="2">
+        <v>0.93368855061783362</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16">
+        <v>357542.03265889653</v>
+      </c>
+      <c r="C16">
         <v>385915</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="2">
         <v>0.9264787133407526</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17">
         <v>183773.7</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>183773.7</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>TR</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>158153.1530507728</v>
-      </c>
-      <c r="C18" t="n">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18">
+        <v>158153.15305077279</v>
+      </c>
+      <c r="C18">
         <v>500419.4</v>
       </c>
-      <c r="D18" t="n">
-        <v>0.3160412107339819</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1633627.475352554</v>
-      </c>
-      <c r="C19" t="n">
+      <c r="D18" s="2">
+        <v>0.31604121073398189</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19">
+        <v>1633627.4753525541</v>
+      </c>
+      <c r="C19">
         <v>3233674.6</v>
       </c>
-      <c r="D19" t="n">
-        <v>0.5051922897104595</v>
+      <c r="D19" s="2">
+        <v>0.50519228971045949</v>
       </c>
     </row>
   </sheetData>
